--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484782_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484782_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.435</v>
+        <v>5.4847</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5811</v>
+        <v>4.1853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8538</v>
+        <v>1.2994</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5612</v>
+        <v>5.285</v>
       </c>
       <c r="H2" t="n">
-        <v>3.139</v>
+        <v>6.4517</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5778</v>
+        <v>-1.1667</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7583</v>
+        <v>5.8057</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0591</v>
+        <v>5.6738</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6992</v>
+        <v>0.1319</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1972</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0798</v>
+        <v>0.7779</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.277</v>
+        <v>-1.2986</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5661</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.0192</v>
+        <v>-3.2079</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4531</v>
+        <v>2.0757</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5759</v>
+        <v>0.7093</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6158</v>
+        <v>0.9649</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0399</v>
+        <v>-0.2556</v>
       </c>
       <c r="V2" t="n">
-        <v>0.864</v>
+        <v>0.6226</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2262</v>
+        <v>0.6226</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3622</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3104</v>
+        <v>4.7227</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9316</v>
+        <v>3.1827</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3788</v>
+        <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>5.285</v>
+        <v>4.1361</v>
       </c>
       <c r="H3" t="n">
-        <v>6.4517</v>
+        <v>2.5255</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1667</v>
+        <v>1.6106</v>
       </c>
       <c r="J3" t="n">
-        <v>5.8057</v>
+        <v>2.9846</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6738</v>
+        <v>2.2187</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1319</v>
+        <v>0.7659</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5207000000000001</v>
+        <v>1.1515</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7779</v>
+        <v>0.3068</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2986</v>
+        <v>0.8447</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1322</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q3" t="n">
         <v>-3.2079</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0757</v>
+        <v>1.5096</v>
       </c>
       <c r="S3" t="n">
-        <v>0.535</v>
+        <v>0.7379</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.6138</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1763</v>
+        <v>0.1241</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6226</v>
+        <v>1.547</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6226</v>
+        <v>2.7922</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8103</v>
+        <v>4.3382</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7237</v>
+        <v>2.1722</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0866</v>
+        <v>2.166</v>
       </c>
       <c r="G4" t="n">
         <v>0.2748</v>
@@ -766,13 +766,13 @@
         <v>2.6418</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5355</v>
+        <v>1.0634</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8999</v>
+        <v>1.3485</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3644</v>
+        <v>-0.285</v>
       </c>
       <c r="V4" t="n">
         <v>1.8678</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4393</v>
+        <v>4.2419</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1109</v>
+        <v>3.6526</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3284</v>
+        <v>0.5893</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1361</v>
+        <v>2.5612</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5255</v>
+        <v>3.139</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6106</v>
+        <v>-0.5778</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9846</v>
+        <v>3.7583</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2187</v>
+        <v>3.0591</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7659</v>
+        <v>0.6992</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1515</v>
+        <v>-1.1972</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3068</v>
+        <v>0.0798</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8447</v>
+        <v>-1.277</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6983</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2079</v>
+        <v>-3.0192</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5096</v>
+        <v>2.4531</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5455</v>
+        <v>1.3828</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.458</v>
+        <v>1.6872</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.3045</v>
       </c>
       <c r="V5" t="n">
-        <v>1.547</v>
+        <v>0.864</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7922</v>
+        <v>1.2262</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2452</v>
+        <v>-0.3622</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3093</v>
+        <v>3.5358</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0747</v>
+        <v>2.8619</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3839</v>
+        <v>0.674</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8121</v>
+        <v>2.49</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8335</v>
+        <v>3.1656</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9786</v>
+        <v>-0.6756</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2762</v>
+        <v>3.4117</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1855</v>
+        <v>2.8103</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.6014</v>
       </c>
       <c r="M6" t="n">
-        <v>1.5358</v>
+        <v>-0.9217</v>
       </c>
       <c r="N6" t="n">
-        <v>0.648</v>
+        <v>0.3553</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8878</v>
+        <v>-1.277</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.2644</v>
+        <v>0.1887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.2079</v>
+        <v>-2.0757</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9435</v>
+        <v>2.2644</v>
       </c>
       <c r="S6" t="n">
-        <v>3.158</v>
+        <v>-0.0069</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9516</v>
+        <v>0.6015</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2064</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6036</v>
+        <v>0.864</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9054</v>
+        <v>0.9244</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3018</v>
+        <v>-0.0604</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7494</v>
+        <v>3.2129</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1764</v>
+        <v>0.1634</v>
       </c>
       <c r="F7" t="n">
-        <v>1.573</v>
+        <v>3.0495</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.207</v>
+        <v>1.4511</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8585</v>
+        <v>0.8257</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0656</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9565</v>
+        <v>-0.2416</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8929</v>
+        <v>0.259</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8494</v>
+        <v>-0.5006</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2506</v>
+        <v>1.6927</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0344</v>
+        <v>0.5666</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2162</v>
+        <v>1.1261</v>
       </c>
       <c r="P7" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="Q7" t="n">
+        <v>-0.3774</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.5096</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.7824</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.1528</v>
+      </c>
+      <c r="V7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.887</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.8242</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.8875999999999999</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.0634</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.2452</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7368</v>
+        <v>2.7048</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1634</v>
+        <v>1.0789</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5734</v>
+        <v>1.6259</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4511</v>
+        <v>-1.207</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8257</v>
+        <v>0.8585</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6254999999999999</v>
+        <v>-2.0656</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2416</v>
+        <v>-0.9565</v>
       </c>
       <c r="K8" t="n">
-        <v>0.259</v>
+        <v>0.8929</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5006</v>
+        <v>-1.8494</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6927</v>
+        <v>-0.2506</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5666</v>
+        <v>-0.0344</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1261</v>
+        <v>-0.2162</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3774</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1534</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7824</v>
+        <v>0.7902</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6289</v>
+        <v>-0.0105</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>M. CHOJNACKI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.1084</v>
+        <v>1.9459</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6725</v>
+        <v>0.8346</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4359</v>
+        <v>1.1113</v>
       </c>
       <c r="G9" t="n">
-        <v>2.49</v>
+        <v>1.205</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1656</v>
+        <v>0.0188</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6756</v>
+        <v>1.1862</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4117</v>
+        <v>0.7511</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8103</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6014</v>
+        <v>0.6666</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9217</v>
+        <v>0.4539</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3553</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.277</v>
+        <v>0.5196</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0757</v>
+        <v>-0.1887</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2644</v>
+        <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4343</v>
+        <v>0.0465</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5879</v>
+        <v>0.2722</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8465</v>
+        <v>-0.2257</v>
       </c>
       <c r="V9" t="n">
-        <v>0.864</v>
+        <v>-0.0604</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-0.0604</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. CHOJNACKI</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4974</v>
+        <v>1.8376</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3861</v>
+        <v>1.7026</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1113</v>
+        <v>0.135</v>
       </c>
       <c r="G10" t="n">
-        <v>1.205</v>
+        <v>1.6776</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0188</v>
+        <v>0.2661</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1862</v>
+        <v>1.4115</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7511</v>
+        <v>2.0963</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.7716</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6666</v>
+        <v>1.3247</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4539</v>
+        <v>-0.4187</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5196</v>
+        <v>0.0868</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7548</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1887</v>
+        <v>-3.0192</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4021</v>
+        <v>0.164</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1764</v>
+        <v>0.7577</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2257</v>
+        <v>-0.5937</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.0604</v>
+        <v>1.5056</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0604</v>
+        <v>-0.3622</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4361</v>
+        <v>1.5497</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1953</v>
+        <v>-1.1464</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2408</v>
+        <v>2.6961</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6776</v>
+        <v>1.8121</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2661</v>
+        <v>0.8335</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4115</v>
+        <v>0.9786</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0963</v>
+        <v>0.2762</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7716</v>
+        <v>0.1855</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3247</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4187</v>
+        <v>1.5358</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5054999999999999</v>
+        <v>0.648</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0868</v>
+        <v>0.8878</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5096</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0192</v>
+        <v>-3.2079</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2375</v>
+        <v>1.3984</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2504</v>
+        <v>0.8798</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4879</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5056</v>
+        <v>0.6036</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8678</v>
+        <v>0.9054</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3622</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5145</v>
+        <v>-0.6686</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.169</v>
+        <v>-1.4026</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6546</v>
+        <v>0.7339</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4903</v>
@@ -1390,13 +1390,13 @@
         <v>1.1322</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4891</v>
+        <v>0.3349</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8288</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3397</v>
+        <v>-0.2604</v>
       </c>
       <c r="V12" t="n">
         <v>-0.7019</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>32.3179</v>
+        <v>32.90560000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>16.6973</v>
+        <v>17.2852</v>
       </c>
       <c r="F13" t="n">
-        <v>15.6205</v>
+        <v>15.6204</v>
       </c>
       <c r="G13" t="n">
         <v>19.1956</v>
@@ -1447,7 +1447,7 @@
         <v>15.7769</v>
       </c>
       <c r="L13" t="n">
-        <v>2.1617</v>
+        <v>2.161700000000001</v>
       </c>
       <c r="M13" t="n">
         <v>1.2567</v>
@@ -1456,25 +1456,25 @@
         <v>2.0115</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7547999999999992</v>
+        <v>-0.7547999999999995</v>
       </c>
       <c r="P13" t="n">
         <v>-1.887</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.75700000000001</v>
+        <v>-20.757</v>
       </c>
       <c r="R13" t="n">
         <v>18.87</v>
       </c>
       <c r="S13" t="n">
-        <v>6.6517</v>
+        <v>7.2396</v>
       </c>
       <c r="T13" t="n">
-        <v>8.705399999999999</v>
+        <v>9.2935</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0538</v>
+        <v>-2.0539</v>
       </c>
       <c r="V13" t="n">
         <v>8.3575</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.063</v>
+        <v>0.1303</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.096</v>
+        <v>-0.2909</v>
       </c>
       <c r="F14" t="n">
-        <v>0.159</v>
+        <v>0.4212</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9513</v>
@@ -1546,13 +1546,13 @@
         <v>0.3774</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0047</v>
+        <v>0.0626</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4267</v>
+        <v>0.2319</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4315</v>
+        <v>-0.1693</v>
       </c>
       <c r="V14" t="n">
         <v>0.6415999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3595</v>
+        <v>-0.3619</v>
       </c>
       <c r="E15" t="n">
         <v>-0.1681</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1914</v>
+        <v>-0.1938</v>
       </c>
       <c r="G15" t="n">
         <v>-1.2538</v>
@@ -1624,13 +1624,13 @@
         <v>1.5096</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3016</v>
+        <v>0.2992</v>
       </c>
       <c r="T15" t="n">
         <v>0.2627</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0388</v>
+        <v>0.0365</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7281</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SERNEGUET GARVI</t>
+          <t>D. RUIZ FRANCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8127</v>
+        <v>-0.8499</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3311</v>
+        <v>-1.6815</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.1438</v>
+        <v>0.8316</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7106</v>
+        <v>-0.4206</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8016</v>
+        <v>-1.1113</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0909</v>
+        <v>0.6907</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5084</v>
+        <v>-0.5662</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1582</v>
+        <v>-0.6073</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3502</v>
+        <v>0.0411</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.219</v>
+        <v>0.1456</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.9597</v>
+        <v>-0.504</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2593</v>
+        <v>0.6496</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.9435</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.9435</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.1322</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.0757</v>
-      </c>
       <c r="S16" t="n">
-        <v>-0.7248</v>
+        <v>-0.4293</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4079</v>
+        <v>-0.1718</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1327</v>
+        <v>-0.2575</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. RUIZ FRANCO</t>
+          <t>J. POPOVIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0267</v>
+        <v>-0.9495</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7789</v>
+        <v>-0.5379</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7522</v>
+        <v>-0.4116</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4206</v>
+        <v>-1.6383</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1113</v>
+        <v>-0.0297</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6907</v>
+        <v>-1.6086</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5662</v>
+        <v>-0.4573</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6073</v>
+        <v>0.7184</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0411</v>
+        <v>-1.1757</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1456</v>
+        <v>-1.181</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.504</v>
+        <v>-0.7482</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6496</v>
+        <v>-0.4329</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9435</v>
+        <v>-0.1887</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6061</v>
+        <v>-0.3945</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2693</v>
+        <v>0.1081</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3368</v>
+        <v>-0.5026</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.4263</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.4263</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>A. SERNEGUET GARVI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0757</v>
+        <v>-0.9534</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0699</v>
+        <v>3.4285</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0058</v>
+        <v>-4.3819</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5822</v>
+        <v>-0.7106</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3154</v>
+        <v>-1.8016</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2668</v>
+        <v>1.0909</v>
       </c>
       <c r="J18" t="n">
-        <v>5.7291</v>
+        <v>2.5084</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4628</v>
+        <v>1.1582</v>
       </c>
       <c r="L18" t="n">
-        <v>3.2663</v>
+        <v>1.3502</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1469</v>
+        <v>-3.219</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1474</v>
+        <v>-2.9597</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0005</v>
+        <v>-0.2593</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.2079</v>
+        <v>0.9435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-6.9819</v>
+        <v>-1.1322</v>
       </c>
       <c r="R18" t="n">
-        <v>3.774</v>
+        <v>2.0757</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3821</v>
+        <v>-0.8655</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8811</v>
+        <v>0.5053</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2632</v>
+        <v>-1.3708</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0679</v>
+        <v>-0.3208</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3018</v>
+        <v>1.547</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3697</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. POPOVIC</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3922</v>
+        <v>-1.5653</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9276</v>
+        <v>-0.5571</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4646</v>
+        <v>-1.0082</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6383</v>
+        <v>3.5822</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0297</v>
+        <v>0.3154</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6086</v>
+        <v>3.2668</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4573</v>
+        <v>5.7291</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7184</v>
+        <v>2.4628</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1757</v>
+        <v>3.2663</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.181</v>
+        <v>-2.1469</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7482</v>
+        <v>-2.1474</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4329</v>
+        <v>0.0005</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5096</v>
+        <v>-3.2079</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1887</v>
+        <v>-6.9819</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6983</v>
+        <v>3.774</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8371</v>
+        <v>-0.8716</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2816</v>
+        <v>0.3939</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5555</v>
+        <v>-1.2655</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.4263</v>
+        <v>-1.0679</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4263</v>
+        <v>-1.3697</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.9915</v>
+        <v>-5.3403</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0492</v>
+        <v>-3.6338</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9423</v>
+        <v>-1.7065</v>
       </c>
       <c r="G20" t="n">
         <v>-3.6073</v>
@@ -2014,13 +2014,13 @@
         <v>3.5853</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6937</v>
+        <v>-1.0426</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8687</v>
+        <v>0.2841</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.5624</v>
+        <v>-1.3267</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0679</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1734</v>
+        <v>-5.3683</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5155</v>
+        <v>-1.7104</v>
       </c>
       <c r="F21" t="n">
         <v>-3.6579</v>
@@ -2092,10 +2092,10 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3281</v>
+        <v>-0.5229</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6771</v>
+        <v>0.4823</v>
       </c>
       <c r="U21" t="n">
         <v>-1.0052</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.9121</v>
+        <v>-6.6462</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5494</v>
+        <v>-2.2571</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3626</v>
+        <v>-4.3891</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3798</v>
@@ -2170,13 +2170,13 @@
         <v>3.774</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5026</v>
+        <v>-1.2367</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1139</v>
+        <v>0.4062</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6165</v>
+        <v>-1.6429</v>
       </c>
       <c r="V22" t="n">
         <v>-3.5393</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.637</v>
+        <v>-9.7638</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.796900000000001</v>
+        <v>-8.212300000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8401</v>
+        <v>-1.5515</v>
       </c>
       <c r="G23" t="n">
         <v>-7.6307</v>
@@ -2248,13 +2248,13 @@
         <v>1.6983</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8741</v>
+        <v>-1.0008</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0335</v>
+        <v>-0.4489</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8406</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-32.3178</v>
+        <v>-31.6683</v>
       </c>
       <c r="E24" t="n">
-        <v>-15.6204</v>
+        <v>-15.6206</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.6973</v>
+        <v>-16.0477</v>
       </c>
       <c r="G24" t="n">
         <v>-19.1954</v>
@@ -2299,7 +2299,7 @@
         <v>-1.407</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.256900000000001</v>
+        <v>-1.2569</v>
       </c>
       <c r="K24" t="n">
         <v>-2.0115</v>
@@ -2326,16 +2326,16 @@
         <v>20.757</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.6517</v>
+        <v>-6.0021</v>
       </c>
       <c r="T24" t="n">
-        <v>2.0537</v>
+        <v>2.0538</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.7056</v>
+        <v>-8.055900000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>-8.3575</v>
+        <v>-8.357500000000002</v>
       </c>
       <c r="W24" t="n">
         <v>2.4524</v>
